--- a/questionnaire_templates/021_pdf_conversion_questionnaire--questionnaire_templates.xlsx
+++ b/questionnaire_templates/021_pdf_conversion_questionnaire--questionnaire_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -615,7 +615,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C26"/>
+  <dimension ref="A1:C21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -818,12 +818,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>zip</t>
+          <t>mp4</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>zip</t>
+          <t>mp4</t>
         </is>
       </c>
     </row>
@@ -835,12 +835,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>mp4</t>
+          <t>avi</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>mp4</t>
+          <t>avi</t>
         </is>
       </c>
     </row>
@@ -852,12 +852,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>avi</t>
+          <t>flv</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>avi</t>
+          <t>flv</t>
         </is>
       </c>
     </row>
@@ -869,12 +869,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>flv</t>
+          <t>m4v</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>flv</t>
+          <t>m4v</t>
         </is>
       </c>
     </row>
@@ -886,12 +886,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>m4v</t>
+          <t>mov</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>m4v</t>
+          <t>mov</t>
         </is>
       </c>
     </row>
@@ -903,12 +903,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>mov</t>
+          <t>mpg</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>mov</t>
+          <t>mpg</t>
         </is>
       </c>
     </row>
@@ -920,146 +920,61 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>mpg</t>
+          <t>mpeg</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>mpg</t>
+          <t>mpeg</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>file_format_choices</t>
+          <t>priority_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>mpeg</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>mpeg</t>
+          <t>low</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>file_format_choices</t>
+          <t>priority_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>avi</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>avi</t>
+          <t>high</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>file_format_choices</t>
+          <t>priority_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>flv</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
-        <is>
-          <t>flv</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>file_format_choices</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>m4v</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>m4v</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>file_format_choices</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>mp4</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>mp4</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>priority_choices</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>priority_choices</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>priority_choices</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
